--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104733_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104733_W31.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8737</v>
+        <v>3.7549</v>
       </c>
       <c r="E2" t="n">
-        <v>5.2267</v>
+        <v>5.9302</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.353</v>
+        <v>-2.1753</v>
       </c>
       <c r="G2" t="n">
-        <v>4.7915</v>
+        <v>4.7817</v>
       </c>
       <c r="H2" t="n">
-        <v>3.0213</v>
+        <v>3.0085</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7702</v>
+        <v>1.7731</v>
       </c>
       <c r="J2" t="n">
-        <v>6.0159</v>
+        <v>5.9954</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6299</v>
+        <v>3.6123</v>
       </c>
       <c r="L2" t="n">
-        <v>2.386</v>
+        <v>2.3832</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.2244</v>
+        <v>-1.2138</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.6086</v>
+        <v>-0.6037</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.6158</v>
+        <v>-0.61</v>
       </c>
       <c r="P2" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1896</v>
+        <v>-0.3031</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.0166</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4451</v>
+        <v>-0.2865</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
       <c r="W2" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.7281</v>
+        <v>-2.7237</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. RUBIO</t>
+          <t>G. CORBALAN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.3052</v>
+        <v>1.9561</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5144</v>
+        <v>3.5395</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7907999999999999</v>
+        <v>-1.5834</v>
       </c>
       <c r="G3" t="n">
-        <v>1.2683</v>
+        <v>2.0172</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7949000000000001</v>
+        <v>3.1716</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4733</v>
+        <v>-1.1543</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7949000000000001</v>
+        <v>4.8508</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7949000000000001</v>
+        <v>3.4884</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>1.3624</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4733</v>
+        <v>-2.8335</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-0.3168</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4733</v>
+        <v>-2.5168</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4544</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-4.5526</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4544</v>
+        <v>2.5039</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5825</v>
+        <v>0.5111</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7195</v>
+        <v>0.5177</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.137</v>
+        <v>-0.0066</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.4764</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.7237</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>E. HAPP</t>
+          <t>J. RUBIO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8131</v>
+        <v>1.8624</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6936</v>
+        <v>1.039</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1196</v>
+        <v>0.8234</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2682</v>
+        <v>1.2667</v>
       </c>
       <c r="H4" t="n">
-        <v>1.079</v>
+        <v>0.7929</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.8109</v>
+        <v>0.4738</v>
       </c>
       <c r="J4" t="n">
-        <v>2.2532</v>
+        <v>0.7929</v>
       </c>
       <c r="K4" t="n">
-        <v>1.5449</v>
+        <v>0.7929</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7083</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9851</v>
+        <v>0.4738</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4659</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5192</v>
+        <v>0.4738</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2272</v>
+        <v>0.4553</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.2719</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.4991</v>
+        <v>0.4553</v>
       </c>
       <c r="S4" t="n">
-        <v>1.3178</v>
+        <v>0.1405</v>
       </c>
       <c r="T4" t="n">
-        <v>1.5528</v>
+        <v>0.2462</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.235</v>
+        <v>-0.1057</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.1594</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1594</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.3322</v>
+        <v>1.5465</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9848</v>
+        <v>1.0933</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3473</v>
+        <v>0.4531</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0076</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.169</v>
+        <v>-0.1719</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1611</v>
+        <v>0.1643</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3113</v>
+        <v>0.3051</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2367</v>
+        <v>0.2306</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3192</v>
+        <v>-0.3127</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4058</v>
+        <v>-0.4025</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0866</v>
+        <v>0.0898</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.1143</v>
+        <v>0.0988</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0315</v>
+        <v>0.0858</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0828</v>
+        <v>0.013</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>0.705</v>
+        <v>0.7025</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>G. CORBALAN</t>
+          <t>E. HAPP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0062</v>
+        <v>0.996</v>
       </c>
       <c r="E6" t="n">
-        <v>2.6762</v>
+        <v>0.9801</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.67</v>
+        <v>0.0159</v>
       </c>
       <c r="G6" t="n">
-        <v>2.024</v>
+        <v>0.2644</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1798</v>
+        <v>1.0696</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1557</v>
+        <v>-0.8052</v>
       </c>
       <c r="J6" t="n">
-        <v>4.8703</v>
+        <v>2.2374</v>
       </c>
       <c r="K6" t="n">
-        <v>3.5029</v>
+        <v>1.5299</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3674</v>
+        <v>0.7075</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.8463</v>
+        <v>-1.9729</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3231</v>
+        <v>-0.4603</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.5231</v>
+        <v>-1.5127</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.0447</v>
+        <v>0.2276</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.5437</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4507</v>
+        <v>0.504</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3785</v>
+        <v>0.8613</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0722</v>
+        <v>-0.3573</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4775</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.7281</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2507</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. AXEL GUDMUNDSSON</t>
+          <t>J. SAMUELS JR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2261</v>
+        <v>0.0168</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.7573</v>
+        <v>-0.8632</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9833</v>
+        <v>0.88</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1618</v>
+        <v>-0.917</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4381</v>
+        <v>-1.324</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5998</v>
+        <v>0.407</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0377</v>
+        <v>-0.7189</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1555</v>
+        <v>-0.5623</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.1178</v>
+        <v>-0.1566</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1241</v>
+        <v>-0.1981</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5936</v>
+        <v>-0.7617</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7177</v>
+        <v>0.5636</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.0487</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1359</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0643</v>
+        <v>-0.5702</v>
       </c>
       <c r="T7" t="n">
-        <v>0.341</v>
+        <v>-0.1443</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2767</v>
+        <v>-0.4259</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="8">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.075</v>
+        <v>-0.0936</v>
       </c>
       <c r="E8" t="n">
-        <v>2.0507</v>
+        <v>1.931</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.1258</v>
+        <v>-2.0246</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2201</v>
+        <v>-0.2178</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2374</v>
+        <v>-0.2357</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0173</v>
+        <v>0.018</v>
       </c>
       <c r="J8" t="n">
-        <v>1.3313</v>
+        <v>1.3295</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1383</v>
+        <v>0.1379</v>
       </c>
       <c r="L8" t="n">
-        <v>1.193</v>
+        <v>1.1916</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5514</v>
+        <v>-1.5472</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3757</v>
+        <v>-0.3736</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1757</v>
+        <v>-1.1736</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S8" t="n">
-        <v>0.782</v>
+        <v>0.7583</v>
       </c>
       <c r="T8" t="n">
-        <v>0.7195</v>
+        <v>0.6015</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0625</v>
+        <v>0.1568</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SAMUELS JR</t>
+          <t>J. AXEL GUDMUNDSSON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2027</v>
+        <v>-0.3592</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1612</v>
+        <v>-1.1677</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9585</v>
+        <v>0.8085</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9198</v>
+        <v>0.168</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.3246</v>
+        <v>-0.4342</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4048</v>
+        <v>0.6021</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.7133</v>
+        <v>0.0358</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.5582</v>
+        <v>0.1551</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1551</v>
+        <v>-0.1194</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2065</v>
+        <v>0.1322</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.7664</v>
+        <v>-0.5893</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5599</v>
+        <v>0.7215</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0447</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0447</v>
+        <v>1.1382</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.782</v>
+        <v>-0.5272</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4479</v>
+        <v>-0.0653</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.334</v>
+        <v>-0.4618</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5456</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. MEINDL</t>
+          <t>D. DIEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2649</v>
+        <v>-0.9091</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0463</v>
+        <v>-0.514</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7815</v>
+        <v>-0.3951</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.7347</v>
+        <v>-2.002</v>
       </c>
       <c r="H10" t="n">
-        <v>0.5087</v>
+        <v>0.6983</v>
       </c>
       <c r="I10" t="n">
-        <v>-3.2435</v>
+        <v>-2.7003</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8963</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1474</v>
+        <v>0.7994</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.0438</v>
+        <v>-0.8718</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8384</v>
+        <v>-1.9296</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6387</v>
+        <v>-0.1011</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1997</v>
+        <v>-1.8285</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4544</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2719</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>2.7262</v>
+        <v>1.3658</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7649</v>
+        <v>0.8653</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8712</v>
+        <v>0.6965</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1064</v>
+        <v>0.1688</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2507</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.2507</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. DIEZ</t>
+          <t>L. MEINDL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1247</v>
+        <v>-0.9108000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.8070000000000001</v>
+        <v>-2.5272</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3177</v>
+        <v>1.6164</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.0024</v>
+        <v>-2.7388</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7018</v>
+        <v>0.5008</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7042</v>
+        <v>-3.2396</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.0625</v>
+        <v>-1.9134</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8070000000000001</v>
+        <v>1.1334</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.8695000000000001</v>
+        <v>-3.0469</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.94</v>
+        <v>-0.8254</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1052</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.8348</v>
+        <v>-0.1927</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2272</v>
+        <v>0.4553</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3631</v>
+        <v>2.7316</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6506</v>
+        <v>0.1255</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3914</v>
+        <v>0.4153</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2591</v>
+        <v>-0.2898</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2472</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.0537</v>
+        <v>-2.3325</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6534</v>
+        <v>-0.1944</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4002</v>
+        <v>-2.1381</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.5605</v>
+        <v>-0.5614</v>
       </c>
       <c r="H12" t="n">
-        <v>1.1864</v>
+        <v>1.1861</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.7469</v>
+        <v>-1.7475</v>
       </c>
       <c r="J12" t="n">
-        <v>0.647</v>
+        <v>0.6395</v>
       </c>
       <c r="K12" t="n">
-        <v>1.2615</v>
+        <v>1.2583</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6145</v>
+        <v>-0.6188</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.2076</v>
+        <v>-1.2009</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.0752</v>
+        <v>-0.0722</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1324</v>
+        <v>-1.1287</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5844</v>
+        <v>0.1394</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1198</v>
+        <v>0.3529</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4645</v>
+        <v>-0.2135</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.8355</v>
+        <v>5.527500000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>8.7212</v>
+        <v>9.246600000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.8857</v>
+        <v>-3.7192</v>
       </c>
       <c r="G13" t="n">
-        <v>2.0684</v>
+        <v>2.0534</v>
       </c>
       <c r="H13" t="n">
-        <v>8.302800000000001</v>
+        <v>8.262</v>
       </c>
       <c r="I13" t="n">
-        <v>-6.2347</v>
+        <v>-6.208600000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>13.5895</v>
+        <v>13.4817</v>
       </c>
       <c r="K13" t="n">
-        <v>12.6608</v>
+        <v>12.5759</v>
       </c>
       <c r="L13" t="n">
-        <v>0.9286000000000003</v>
+        <v>0.9056999999999997</v>
       </c>
       <c r="M13" t="n">
-        <v>-11.5215</v>
+        <v>-11.4281</v>
       </c>
       <c r="N13" t="n">
-        <v>-4.358199999999999</v>
+        <v>-4.3138</v>
       </c>
       <c r="O13" t="n">
-        <v>-7.1632</v>
+        <v>-7.1143</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2719</v>
+        <v>2.276299999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.7671</v>
+        <v>-14.7961</v>
       </c>
       <c r="R13" t="n">
-        <v>17.039</v>
+        <v>17.0724</v>
       </c>
       <c r="S13" t="n">
-        <v>1.0411</v>
+        <v>1.7424</v>
       </c>
       <c r="T13" t="n">
-        <v>2.873199999999999</v>
+        <v>3.551</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.832100000000001</v>
+        <v>-1.8085</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5455999999999998</v>
+        <v>-0.5448</v>
       </c>
       <c r="W13" t="n">
-        <v>7.0258</v>
+        <v>7.0102</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.5714</v>
+        <v>-7.5549</v>
       </c>
     </row>
     <row r="14">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0796</v>
+        <v>6.1092</v>
       </c>
       <c r="E14" t="n">
-        <v>6.1718</v>
+        <v>6.738</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0922</v>
+        <v>-0.6288</v>
       </c>
       <c r="G14" t="n">
-        <v>2.7444</v>
+        <v>2.7433</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5281</v>
+        <v>0.5334</v>
       </c>
       <c r="I14" t="n">
-        <v>2.2162</v>
+        <v>2.2099</v>
       </c>
       <c r="J14" t="n">
-        <v>4.5513</v>
+        <v>4.536</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2638</v>
+        <v>2.258</v>
       </c>
       <c r="L14" t="n">
-        <v>2.2875</v>
+        <v>2.278</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8069</v>
+        <v>-1.7927</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.7357</v>
+        <v>-1.7246</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.0712</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7262</v>
+        <v>2.7316</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4376</v>
+        <v>-0.4065</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5173</v>
+        <v>0.0717</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9203</v>
+        <v>-0.4782</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="W14" t="n">
-        <v>3.2738</v>
+        <v>3.2684</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. AUDIGE</t>
+          <t>J. WEBB III</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.294</v>
+        <v>4.4995</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3491</v>
+        <v>4.27</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.0551</v>
+        <v>0.2295</v>
       </c>
       <c r="G15" t="n">
-        <v>5.3517</v>
+        <v>2.365</v>
       </c>
       <c r="H15" t="n">
-        <v>1.3314</v>
+        <v>-3.0048</v>
       </c>
       <c r="I15" t="n">
-        <v>4.0204</v>
+        <v>5.3698</v>
       </c>
       <c r="J15" t="n">
-        <v>6.6431</v>
+        <v>4.7037</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0821</v>
+        <v>-0.5763</v>
       </c>
       <c r="L15" t="n">
-        <v>3.561</v>
+        <v>5.28</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2914</v>
+        <v>-2.3387</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.7507</v>
+        <v>-2.4285</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4594</v>
+        <v>0.0898</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3631</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4078</v>
+        <v>-2.2763</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0447</v>
+        <v>2.7316</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.149</v>
+        <v>-0.1127</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1138</v>
+        <v>0.0507</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2628</v>
+        <v>-0.1634</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5456</v>
+        <v>1.792</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.792</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.5456</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. WEBB III</t>
+          <t>C. AUDIGE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2575</v>
+        <v>3.3824</v>
       </c>
       <c r="E16" t="n">
-        <v>3.5868</v>
+        <v>3.3198</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3292</v>
+        <v>0.0626</v>
       </c>
       <c r="G16" t="n">
-        <v>2.3631</v>
+        <v>5.3463</v>
       </c>
       <c r="H16" t="n">
-        <v>-3.0114</v>
+        <v>1.3324</v>
       </c>
       <c r="I16" t="n">
-        <v>5.3745</v>
+        <v>4.0139</v>
       </c>
       <c r="J16" t="n">
-        <v>4.7185</v>
+        <v>6.6231</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5695</v>
+        <v>3.0714</v>
       </c>
       <c r="L16" t="n">
-        <v>5.2879</v>
+        <v>3.5517</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.3554</v>
+        <v>-1.2769</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.442</v>
+        <v>-1.739</v>
       </c>
       <c r="O16" t="n">
-        <v>0.0866</v>
+        <v>0.4622</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4544</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2719</v>
+        <v>-3.4145</v>
       </c>
       <c r="R16" t="n">
-        <v>2.7262</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.3562</v>
+        <v>-0.0534</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6561</v>
+        <v>0.1111</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7</v>
+        <v>-0.1645</v>
       </c>
       <c r="V16" t="n">
-        <v>1.7963</v>
+        <v>-0.5447</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7963</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="17">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1947</v>
+        <v>2.1859</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5926</v>
+        <v>2.7018</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3978</v>
+        <v>-0.5158</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3853</v>
+        <v>0.3834</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.6612</v>
+        <v>-0.6606</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0465</v>
+        <v>1.0439</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7095</v>
+        <v>1.703</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0752</v>
+        <v>0.0722</v>
       </c>
       <c r="L17" t="n">
-        <v>1.6344</v>
+        <v>1.6308</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3242</v>
+        <v>-1.3196</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.7363</v>
+        <v>-0.7328</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5878</v>
+        <v>-0.5868</v>
       </c>
       <c r="P17" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4178</v>
+        <v>-0.425</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2082</v>
+        <v>-0.0907</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2096</v>
+        <v>-0.3344</v>
       </c>
       <c r="V17" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9329</v>
+        <v>0.9535</v>
       </c>
       <c r="E18" t="n">
-        <v>0.7872</v>
+        <v>0.5423</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1457</v>
+        <v>0.4112</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2829</v>
+        <v>-0.2812</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2382</v>
+        <v>-1.2378</v>
       </c>
       <c r="I18" t="n">
-        <v>0.9553</v>
+        <v>0.9566</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0975</v>
+        <v>0.092</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1262</v>
+        <v>-0.1314</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2237</v>
+        <v>0.2234</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3804</v>
+        <v>-0.3733</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.112</v>
+        <v>-1.1064</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7317</v>
+        <v>0.7331</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6936</v>
+        <v>0.7096</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5302</v>
+        <v>0.2925</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1633</v>
+        <v>0.4171</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="19">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8188</v>
+        <v>0.9362</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0196</v>
+        <v>0.6539</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2008</v>
+        <v>0.2823</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.4814</v>
+        <v>-0.4805</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5613</v>
+        <v>-0.5576</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0799</v>
+        <v>0.0771</v>
       </c>
       <c r="J19" t="n">
-        <v>0.1863</v>
+        <v>0.1781</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0924</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0939</v>
+        <v>0.0887</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6677</v>
+        <v>-0.6587</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6536999999999999</v>
+        <v>-0.6471</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.014</v>
+        <v>-0.0116</v>
       </c>
       <c r="P19" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3914</v>
+        <v>0.5062</v>
       </c>
       <c r="T19" t="n">
-        <v>0.8333</v>
+        <v>0.4757</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4419</v>
+        <v>0.0305</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0293</v>
+        <v>-0.418</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.07190000000000001</v>
+        <v>-0.1949</v>
       </c>
       <c r="F20" t="n">
-        <v>0.0427</v>
+        <v>-0.223</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7731</v>
+        <v>-0.7685999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0188</v>
+        <v>-0.0149</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.7543</v>
+        <v>-0.7537</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5534</v>
+        <v>-0.5545</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0864</v>
+        <v>0.0862</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6398</v>
+        <v>-0.6407</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.2197</v>
+        <v>-0.2141</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1052</v>
+        <v>-0.1011</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1145</v>
+        <v>-0.113</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6992</v>
+        <v>0.302</v>
       </c>
       <c r="T20" t="n">
-        <v>0.322</v>
+        <v>0.2018</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3771</v>
+        <v>0.1002</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.4896</v>
+        <v>-1.7735</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.1235</v>
+        <v>-0.4919</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.366</v>
+        <v>-1.2816</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.6167</v>
+        <v>-2.6118</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.511</v>
+        <v>-0.5036</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.1057</v>
+        <v>-2.1083</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9121</v>
+        <v>-0.919</v>
       </c>
       <c r="K21" t="n">
-        <v>0.8641</v>
+        <v>0.8618</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.7762</v>
+        <v>-1.7808</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7046</v>
+        <v>-1.6929</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.375</v>
+        <v>-1.3654</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3295</v>
+        <v>-0.3275</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9</v>
+        <v>0.6108</v>
       </c>
       <c r="T21" t="n">
-        <v>0.8333</v>
+        <v>0.4757</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0667</v>
+        <v>0.135</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.7756</v>
+        <v>-2.517</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9578</v>
+        <v>-0.9663</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.8178</v>
+        <v>-1.5506</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.2548</v>
+        <v>-2.252</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.7582</v>
+        <v>-1.7526</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.4966</v>
+        <v>-0.4994</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.9832</v>
+        <v>-0.9892</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4433</v>
+        <v>-0.4449</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.5399</v>
+        <v>-0.5443</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2716</v>
+        <v>-1.2628</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3149</v>
+        <v>-1.3077</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0433</v>
+        <v>0.0449</v>
       </c>
       <c r="P22" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1161</v>
+        <v>0.3692</v>
       </c>
       <c r="T22" t="n">
-        <v>0.0254</v>
+        <v>0.0229</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0907</v>
+        <v>0.3463</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.2568</v>
+        <v>-6.6237</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.2431</v>
+        <v>-5.8987</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0137</v>
+        <v>-0.7249</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.2003</v>
+        <v>-3.1975</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5613</v>
+        <v>-0.5576</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.639</v>
+        <v>-2.6399</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.3494</v>
+        <v>-2.3517</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.3667</v>
+        <v>-2.3689</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8508</v>
+        <v>-0.8458</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5786</v>
+        <v>-0.5749</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2723</v>
+        <v>-0.271</v>
       </c>
       <c r="P23" t="n">
-        <v>-3.1806</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8759</v>
+        <v>-0.2393</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4858</v>
+        <v>-0.1326</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3901</v>
+        <v>-0.1067</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.861700000000001</v>
+        <v>-9.196099999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.2249</v>
+        <v>-6.9547</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.6369</v>
+        <v>-2.2414</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.3034</v>
+        <v>-3.2995</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8408</v>
+        <v>-1.8383</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.4626</v>
+        <v>-1.4612</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5867</v>
+        <v>-1.5934</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.9842</v>
+        <v>-0.99</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.6025</v>
+        <v>-0.6035</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7167</v>
+        <v>-1.7061</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8566</v>
+        <v>-0.8483000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8601</v>
+        <v>-0.8578</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.3166</v>
+        <v>-4.325</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5.6797</v>
+        <v>-5.6908</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S24" t="n">
-        <v>0.3951</v>
+        <v>0.0626</v>
       </c>
       <c r="T24" t="n">
-        <v>1.0415</v>
+        <v>0.3295</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6464</v>
+        <v>-0.2669</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-4.835500000000003</v>
+        <v>-2.4616</v>
       </c>
       <c r="E25" t="n">
-        <v>3.885900000000003</v>
+        <v>3.719299999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.7211</v>
+        <v>-6.1805</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.068099999999999</v>
+        <v>-2.053099999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.302700000000002</v>
+        <v>-8.262</v>
       </c>
       <c r="I25" t="n">
-        <v>6.234600000000002</v>
+        <v>6.208699999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>11.5214</v>
+        <v>11.4281</v>
       </c>
       <c r="K25" t="n">
-        <v>4.3581</v>
+        <v>4.3136</v>
       </c>
       <c r="L25" t="n">
-        <v>7.1633</v>
+        <v>7.1144</v>
       </c>
       <c r="M25" t="n">
-        <v>-13.5894</v>
+        <v>-13.4816</v>
       </c>
       <c r="N25" t="n">
-        <v>-12.6607</v>
+        <v>-12.5758</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9283999999999999</v>
+        <v>-0.9057999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.2719</v>
+        <v>-2.276199999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-17.039</v>
+        <v>-17.0725</v>
       </c>
       <c r="R25" t="n">
-        <v>14.767</v>
+        <v>14.7962</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0411</v>
+        <v>1.3235</v>
       </c>
       <c r="T25" t="n">
-        <v>1.8321</v>
+        <v>1.8083</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.8733</v>
+        <v>-0.4849999999999998</v>
       </c>
       <c r="V25" t="n">
-        <v>0.5455999999999996</v>
+        <v>0.5447000000000004</v>
       </c>
       <c r="W25" t="n">
-        <v>7.5715</v>
+        <v>7.555000000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.025899999999999</v>
+        <v>-7.0101</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104733_W31.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104733_W31.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-2.7237</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>0</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-7.5549</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104733_W31.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-7.0101</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
